--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T12:55:00+00:00</t>
+    <t>2026-07-09T14:22:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T14:22:57+00:00</t>
+    <t>2026-07-10T07:56:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T07:56:32+00:00</t>
+    <t>2026-07-10T08:06:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T08:06:49+00:00</t>
+    <t>2026-07-13T17:37:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T17:37:40+00:00</t>
+    <t>2026-07-13T18:45:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T18:45:44+00:00</t>
+    <t>2026-07-15T08:24:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T08:24:19+00:00</t>
+    <t>2026-07-15T09:46:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T09:46:46+00:00</t>
+    <t>2026-07-15T12:12:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T12:12:36+00:00</t>
+    <t>2026-07-15T12:23:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T12:23:19+00:00</t>
+    <t>2026-07-15T13:30:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T13:30:57+00:00</t>
+    <t>2026-07-15T14:20:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T14:20:54+00:00</t>
+    <t>2026-07-15T14:44:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T14:44:09+00:00</t>
+    <t>2026-07-15T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T16:26:13+00:00</t>
+    <t>2026-07-15T16:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T16:58:30+00:00</t>
+    <t>2026-07-15T17:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T17:15:57+00:00</t>
+    <t>2026-07-16T08:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T08:32:04+00:00</t>
+    <t>2026-07-20T10:20:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T10:20:59+00:00</t>
+    <t>2026-07-20T14:00:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T14:00:59+00:00</t>
+    <t>2026-07-22T08:48:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T08:48:12+00:00</t>
+    <t>2026-07-22T09:17:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:17:02+00:00</t>
+    <t>2026-07-22T09:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:38:06+00:00</t>
+    <t>2026-07-22T12:21:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:21:08+00:00</t>
+    <t>2026-07-22T13:08:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T13:08:28+00:00</t>
+    <t>2026-07-22T13:46:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T13:46:01+00:00</t>
+    <t>2026-07-22T14:02:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T14:02:04+00:00</t>
+    <t>2026-07-22T14:55:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T14:55:39+00:00</t>
+    <t>2026-07-22T15:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T15:36:30+00:00</t>
+    <t>2026-07-22T16:29:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T16:29:14+00:00</t>
+    <t>2026-07-22T16:42:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T16:42:04+00:00</t>
+    <t>2026-07-23T08:48:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T08:48:51+00:00</t>
+    <t>2026-07-23T09:00:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T09:00:10+00:00</t>
+    <t>2026-07-28T14:01:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T14:01:02+00:00</t>
+    <t>2026-07-28T14:17:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T14:17:02+00:00</t>
+    <t>2026-09-09T13:38:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T13:38:12+00:00</t>
+    <t>2026-09-09T14:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
+++ b/feature/testEDN/ig/StructureDefinition-sas-sos-location-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:33:52+00:00</t>
+    <t>2026-09-09T14:45:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
